--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6502_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6502_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,260 +479,255 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>FSW1_CSANG@LEG1</t>
+          <t>FSW1_MINR@LEG1</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>FSW1_MINR@LEG1</t>
+          <t>FSW1_THDL@LEG1</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>FSW1_THDL@LEG1</t>
+          <t>FSW1_RELANG@LEG1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>FSW1_RELANG@LEG1</t>
+          <t>FSW1_RELR@LEG1</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>FSW1_RELR@LEG1</t>
+          <t>FSW1_STEMR@LEG1</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>FSW1_STEMR@LEG1</t>
+          <t>FSW1_HEADL@LEG1</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FSW1_HEADL@LEG1</t>
+          <t>NUTHEX1@NUTHEX1</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>NUTHEX1@NUTHEX1</t>
+          <t>DEPTH@NUTCUT1</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT1</t>
+          <t>M2@LEG2</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>M2@LEG2</t>
+          <t>BODYR@LEG2</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>BODYR@LEG2</t>
+          <t>THDMAJR_B2@LEG2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>THDMAJR_B2@LEG2</t>
+          <t>FSM2_THDL@LEG2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSM2_THDL@LEG2</t>
+          <t>FSMCHANG2@LEG2</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSMCHANG2@LEG2</t>
+          <t>FSM2_FACER@LEG2</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSM2_FACER@LEG2</t>
+          <t>FSM2_GRVOR@LEG2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSM2_GRVOR@LEG2</t>
+          <t>FSM2_GRVD@LEG2</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>FSM2_GRVD@LEG2</t>
+          <t>FSM2_GRVIR@LEG2</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>FSM2_GRVIR@LEG2</t>
+          <t>D1@BORE1</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>D1@BORE1</t>
+          <t>DEPTH@BORECUT1</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT1</t>
+          <t>D2@BORE2</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>D2@BORE2</t>
+          <t>DEPTH@BORECUT2</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT2</t>
+          <t>HELIXDIA@HELIXSK_1</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_1</t>
+          <t>HEIGHT@HELIX_1</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_1</t>
+          <t>PITCH@HELIX_1</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_1</t>
+          <t>PROF_R@THDPROF_1</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_1</t>
+          <t>APEXR@THDPROF_1</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_1</t>
+          <t>PROF_AX@THDPROF_1</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_1</t>
+          <t>THDDIA@THD_End2</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>THDDIA@THD_End2</t>
+          <t>THDPITCH@THD_End2</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End2</t>
+          <t>DEPTH@THD_End2</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>DEPTH@THD_End2</t>
+          <t>Profile_Height@THD_End2_PROF</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>Profile_Height@THD_End2_PROF</t>
+          <t>Profile_Land@THD_End2_PROF</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>Profile_Land@THD_End2_PROF</t>
+          <t>THDPITCH@THD_End2_PROF</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End2_PROF</t>
+          <t>HEXAF@HEX1</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX1</t>
+          <t>HEXL@HEX1_BODY</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>HEXL@HEX1_BODY</t>
+          <t>HEXAF@HEX2</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX2</t>
+          <t>HEXL@HEX2_BODY</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>HEXL@HEX2_BODY</t>
+          <t>PUCK_HB@PUCK</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>PUCK_HB@PUCK</t>
+          <t>PUCK_HT@PUCK</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>PUCK_HT@PUCK</t>
+          <t>PUCK_R1B@PUCK</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>PUCK_R1B@PUCK</t>
+          <t>PUCK_R1T@PUCK</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>PUCK_R1T@PUCK</t>
+          <t>PUCK_XC@PUCK</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>PUCK_XC@PUCK</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@End1_Thread</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>$PRP@End1_Thread</t>
+          <t>$PRP@End2_Thread</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>$PRP@End2_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -781,175 +776,172 @@
         <v>0.4095</v>
       </c>
       <c r="N2" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="P2" t="n">
         <v>45</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.7448399999999999</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AL2" t="n">
         <v>0.37242</v>
       </c>
-      <c r="P2" t="n">
-        <v>0.36882</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>45</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.4165</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3725</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AM2" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AY2" t="n">
         <v>0.375</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.45725</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.3595</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.3145</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.2125</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.753</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.7448399999999999</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.4059</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.37242</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.753</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.45725</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.03383</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.01562</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.296</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.375</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.375</v>
+        <v>0.21601</v>
       </c>
       <c r="BB2" t="n">
         <v>0.21601</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.21601</v>
-      </c>
-      <c r="BD2" t="n">
         <v>0.43251</v>
       </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>FS6502-08-08-FG</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>FS6502-08-08-FG</t>
+          <t>ORFS 45 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>ORFS 45 deg Male Face Seal x Female Face Seal Swivel Elbow, 13/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>FS6502</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>FS6502</t>
+          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "L1 LGTH" = "0.80" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); L2@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "L2 LGTH" = "1.32" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face along the 45 deg axis (NEW column: mapping to Air-Way L52 not confirmed); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "C HEX" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); Q-FS-NUT: = Air-Way FF318-8 S 0.94 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "JJ FLATS" = "0.75" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "B THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "B THREAD" "13/16-16" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSM -08 bore on 73 Air-Way row(s) in 19 tables: 0.37 x73 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSSW -08 bore on 5 Air-Way row(s) in 3 tables: 0.35 x5 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); swivel leg length L2 (Brennan ORFS catalog p9 "L2 LGTH") read as the crossing -&gt; the stem SEAL face, as measured where Brennan STEPs exist (FS6500 AAA = L21, FS6565 L45; ASSUMPTION - no BRENNAN_FS6502 STEP); the swivel on the X leg and the male face seal on the 45deg leg, as 6502; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "L1 LGTH" = "0.80" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); L2@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "L2 LGTH" = "1.32" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face along the 45 deg axis (NEW column: mapping to Air-Way L52 not confirmed); mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "C HEX" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); Q-FS-NUT: = Air-Way FF318-8 S 0.94 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "JJ FLATS" = "0.75" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 500.2, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: no row of this table has both an Air-Way and a Brennan value (drawing mapping only; cross-check in evidence/crosscheck.txt); THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "A THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -08 = 0.8125 (PLAN.md s2 FS_THR / the -08 thread of every staged ORFS row); = Brennan "B THREAD" "13/16-16" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "A THREAD" "13/16-16" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t02 "FS6502-FG MFS-FFSS 45 DEG ELBOW" row FS6502-08-08-FG col "B THREAD" "13/16-16" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSM -08 bore on 73 Air-Way row(s) in 19 tables: 0.37 x73 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSSW -08 bore on 5 Air-Way row(s) in 3 tables: 0.35 x5 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); swivel leg length L2 (Brennan ORFS catalog p9 "L2 LGTH") read as the crossing -&gt; the stem SEAL face, as measured where Brennan STEPs exist (FS6500 AAA = L21, FS6565 L45; ASSUMPTION - no BRENNAN_FS6502 STEP); the swivel on the X leg and the male face seal on the 45deg leg, as 6502; each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on L2 LGTH=1.32 vs Air-Way L52=1.49 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6502 is used only where Brennan FS6502-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5587 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6502-08-08-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
-        <is>
-          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on L2 LGTH=1.32 vs Air-Way L52=1.49 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6502 is used only where Brennan FS6502-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5587 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6502-08-08-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
         <is>
           <t>FS6502-08-08-FG</t>
         </is>
